--- a/june 2026/LMT_JUNE_26/Al-fatah Zubaida Traders.xlsx
+++ b/june 2026/LMT_JUNE_26/Al-fatah Zubaida Traders.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B5AD6-118D-4BF8-8635-A399F346D9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6B3D11-D8F1-43E2-B262-BEB0677728EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,8 +12,8 @@
     <sheet name="Cust. Price List" sheetId="6" r:id="rId2"/>
     <sheet name="Format" sheetId="15" r:id="rId3"/>
     <sheet name="1" sheetId="16" r:id="rId4"/>
-    <sheet name="3" sheetId="19" r:id="rId5"/>
-    <sheet name="2" sheetId="17" r:id="rId6"/>
+    <sheet name="2" sheetId="17" r:id="rId5"/>
+    <sheet name="3" sheetId="19" r:id="rId6"/>
     <sheet name="4" sheetId="18" r:id="rId7"/>
     <sheet name="5" sheetId="20" r:id="rId8"/>
     <sheet name="6" sheetId="21" r:id="rId9"/>
@@ -3421,7 +3421,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3449,7 +3449,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4668,7 +4668,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4696,7 +4696,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5915,7 +5915,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5943,7 +5943,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7162,7 +7162,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7190,7 +7190,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8409,7 +8409,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8437,7 +8437,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9656,7 +9656,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9684,7 +9684,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10903,7 +10903,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10931,7 +10931,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12150,7 +12150,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12178,7 +12178,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13397,7 +13397,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13425,7 +13425,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14644,7 +14644,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14672,7 +14672,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18641,7 +18641,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18669,7 +18669,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19885,7 +19885,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19913,7 +19913,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21128,7 +21128,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21156,7 +21156,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22371,7 +22371,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22399,7 +22399,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23619,7 +23619,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23647,7 +23647,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23944,11 +23944,11 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>41970</v>
+        <v>104925</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23960,23 +23960,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>7554.5999999999995</v>
+        <v>18886.5</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>34415.4</v>
+        <v>86038.5</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>6194.7719999999999</v>
+        <v>15486.93</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>203.05086</v>
+        <v>507.62715000000003</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>40813.222860000002</v>
+        <v>102033.05714999999</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -24018,11 +24018,11 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>62955</v>
+        <v>125910</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
@@ -24034,23 +24034,23 @@
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>11331.9</v>
+        <v>22663.8</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>51623.1</v>
+        <v>103246.2</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>9292.1579999999994</v>
+        <v>18584.315999999999</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>304.57629000000003</v>
+        <v>609.15258000000006</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>61219.834289999999</v>
+        <v>122439.66858</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="U17" s="163">
         <f>+'3'!P35</f>
-        <v>0</v>
+        <v>638096.79793500004</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -24092,11 +24092,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18</f>
-        <v>2800</v>
+        <v>4600</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>146895</v>
+        <v>241327.5</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
@@ -24108,23 +24108,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>26441.1</v>
+        <v>43438.95</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>120453.9</v>
+        <v>197888.55</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>21681.701999999997</v>
+        <v>35619.938999999998</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>710.67800999999997</v>
+        <v>1167.542445</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>142846.28000999999</v>
+        <v>234676.031445</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24162,11 +24162,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>1800</v>
+        <v>4200</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>130752</v>
+        <v>305088</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24178,23 +24178,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>23535.360000000001</v>
+        <v>54915.839999999997</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>107216.64</v>
+        <v>250172.16</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>19298.995199999998</v>
+        <v>45030.988799999992</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>632.57817599999998</v>
+        <v>1476.0157439999998</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>127148.21337599999</v>
+        <v>296679.16454399994</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24232,11 +24232,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>87168</v>
+        <v>217920</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -24248,23 +24248,23 @@
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>15690.24</v>
+        <v>39225.599999999999</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>71477.759999999995</v>
+        <v>178694.39999999999</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>12865.996799999999</v>
+        <v>32164.991999999998</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>421.71878399999997</v>
+        <v>1054.2969599999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>84765.475583999985</v>
+        <v>211913.68896</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24302,11 +24302,11 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>3600</v>
+        <v>5400</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>261504</v>
+        <v>392256</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -24318,23 +24318,23 @@
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>47070.720000000001</v>
+        <v>70606.080000000002</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>214433.28</v>
+        <v>321649.91999999998</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>38597.990399999995</v>
+        <v>57896.985599999993</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>1265.156352</v>
+        <v>1897.734528</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>254296.42675199997</v>
+        <v>381444.640128</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24562,7 +24562,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>285</v>
+        <v>540</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24573,11 +24573,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>11400</v>
+        <v>21600</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>731244</v>
+        <v>1387426.5</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24589,23 +24589,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>131623.91999999998</v>
+        <v>249736.77000000002</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>599620.07999999996</v>
+        <v>1137689.73</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>107931.61439999999</v>
+        <v>204784.15139999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>3537.758472</v>
+        <v>6712.3694070000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>711089.45287199994</v>
+        <v>1349186.2508069999</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>711089.45287200005</v>
+        <v>1349186.2508070001</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24846,7 +24846,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>731244</v>
+        <v>1387426.5</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24867,7 +24867,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>131623.91999999998</v>
+        <v>249736.77000000002</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24910,7 +24910,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>599620.08000000007</v>
+        <v>1137689.73</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>107931.61439999999</v>
+        <v>204784.15139999997</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24957,7 +24957,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>707551.69440000004</v>
+        <v>1342473.8813999998</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>17688.792360000003</v>
+        <v>33561.847034999999</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24992,7 +24992,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>725240.48676</v>
+        <v>1376035.7284349999</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25163,8 +25163,7 @@
       <c r="L4" s="230"/>
       <c r="M4" s="230"/>
       <c r="N4" s="244">
-        <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25191,8 +25190,8 @@
       <c r="L5" s="230"/>
       <c r="M5" s="230"/>
       <c r="N5" s="244">
-        <f ca="1">N4-1</f>
-        <v>46211</v>
+        <f>N4-1</f>
+        <v>46191</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -26339,7 +26338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26386,7 +26385,7 @@
       <c r="L3" s="230"/>
       <c r="M3" s="230"/>
       <c r="N3" s="231">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O3" s="231"/>
       <c r="P3" s="231"/>
@@ -26414,7 +26413,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26442,7 +26441,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -26534,7 +26533,7 @@
       <c r="A10" s="228" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="168" t="s">
+      <c r="B10" s="75" t="s">
         <v>104</v>
       </c>
       <c r="C10" s="75"/>
@@ -26609,7 +26608,7 @@
     </row>
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="229"/>
-      <c r="B13" s="56">
+      <c r="B13" s="167">
         <v>300426949714</v>
       </c>
       <c r="J13" s="78"/>
@@ -27490,6 +27489,1252 @@
       <c r="P35" s="159">
         <f>P33+P34</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="160" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="206"/>
+      <c r="I36" s="207"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="209"/>
+    </row>
+    <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="B28:L34"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>$XFD$12:$XFD$17</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{00000000-0002-0000-0400-000001000000}">
+      <formula1>$XFC$6:$XFC$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0400-000002000000}">
+      <formula1>$XFC$3:$XFC$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000003000000}">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$6:$B$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>N6:P6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:XFD37"/>
+  <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.453125" customWidth="1"/>
+    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.81640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
+      <c r="A2" s="246" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+    </row>
+    <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="231" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="231"/>
+      <c r="C3" s="231"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="71"/>
+      <c r="K3" s="230" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="230"/>
+      <c r="M3" s="230"/>
+      <c r="N3" s="231">
+        <v>4</v>
+      </c>
+      <c r="O3" s="231"/>
+      <c r="P3" s="231"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="71"/>
+      <c r="XFC3" t="s">
+        <v>48</v>
+      </c>
+      <c r="XFD3" s="72">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="231" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="231"/>
+      <c r="C4" s="231"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
+      <c r="K4" s="230" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="230"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="244">
+        <v>46181</v>
+      </c>
+      <c r="O4" s="244"/>
+      <c r="P4" s="244"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="71"/>
+      <c r="XFC4" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="XFD4" s="72">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="253" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="253"/>
+      <c r="C5" s="253"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="71"/>
+      <c r="K5" s="230" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="230"/>
+      <c r="M5" s="230"/>
+      <c r="N5" s="244">
+        <f>N4-1</f>
+        <v>46180</v>
+      </c>
+      <c r="O5" s="231"/>
+      <c r="P5" s="231"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="71"/>
+    </row>
+    <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="230" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="230"/>
+      <c r="C6" s="230"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="74"/>
+      <c r="K6" s="230" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="230"/>
+      <c r="M6" s="230"/>
+      <c r="N6" s="243" t="s">
+        <v>101</v>
+      </c>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="74"/>
+      <c r="XFC6" t="s">
+        <v>53</v>
+      </c>
+      <c r="XFD6" s="2">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="230"/>
+      <c r="B7" s="230"/>
+      <c r="C7" s="230"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="74"/>
+      <c r="K7" s="230"/>
+      <c r="L7" s="230"/>
+      <c r="M7" s="230"/>
+      <c r="N7" s="243"/>
+      <c r="O7" s="243"/>
+      <c r="P7" s="243"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="74"/>
+      <c r="XFC7" t="s">
+        <v>54</v>
+      </c>
+      <c r="XFD7" s="2">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="242"/>
+      <c r="B8" s="242"/>
+      <c r="C8" s="242"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="74"/>
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="243"/>
+      <c r="O8" s="243"/>
+      <c r="P8" s="243"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="74"/>
+    </row>
+    <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="A9" s="242"/>
+      <c r="B9" s="242"/>
+      <c r="C9" s="242"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="74"/>
+      <c r="K9" s="230"/>
+      <c r="L9" s="230"/>
+      <c r="M9" s="230"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="243"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="74"/>
+      <c r="XFD9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="A10" s="228" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="168" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="75"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
+      <c r="K10" s="230" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="230"/>
+      <c r="M10" s="230"/>
+      <c r="N10" s="231" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="231"/>
+      <c r="P10" s="231"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="71"/>
+      <c r="XFD10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="A11" s="228"/>
+      <c r="B11" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="77" t="str">
+        <f>IF($O34&gt;2.49%,"No","Yes")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
+      <c r="K11" s="230" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="230"/>
+      <c r="M11" s="230"/>
+      <c r="N11" s="231" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="231"/>
+      <c r="P11" s="231"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="71"/>
+    </row>
+    <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="228" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="77" t="str">
+        <f>IF($O32&gt;21.99%,"No","Yes")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
+      <c r="K12" s="230" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="230"/>
+      <c r="M12" s="230"/>
+      <c r="N12" s="231"/>
+      <c r="O12" s="231"/>
+      <c r="P12" s="231"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="71"/>
+      <c r="XFD12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="229"/>
+      <c r="B13" s="56">
+        <v>300426949714</v>
+      </c>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="79">
+        <v>0.05</v>
+      </c>
+      <c r="XFD13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="232" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="233"/>
+      <c r="C14" s="236" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="82" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="248" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="249"/>
+      <c r="I14" s="250" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="248" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="252"/>
+      <c r="L14" s="249"/>
+      <c r="M14" s="250" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="P14" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="XFD14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19 16383:16384" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="234"/>
+      <c r="B15" s="235"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="88" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="89" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="251"/>
+      <c r="J15" s="88" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="90" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="183">
+        <v>0.18</v>
+      </c>
+      <c r="M15" s="251"/>
+      <c r="N15" s="91">
+        <f>IF(B12="Registered",18%,22%)</f>
+        <v>0.18</v>
+      </c>
+      <c r="O15" s="92">
+        <f>IF(B11="Filer",0.5%,2.5%)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P15" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="XFD15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="A16" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="95" t="str">
+        <f>VLOOKUP($A16,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v xml:space="preserve">Meat Masala </v>
+      </c>
+      <c r="C16" s="96">
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,3,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D16" s="97">
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E16" s="97">
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F16" s="98">
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G16" s="99"/>
+      <c r="H16" s="100">
+        <v>1200</v>
+      </c>
+      <c r="I16" s="101">
+        <f>(G16*D16)*F16+H16*F16</f>
+        <v>62955</v>
+      </c>
+      <c r="J16" s="102">
+        <v>0</v>
+      </c>
+      <c r="K16" s="103">
+        <f>I16*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="104">
+        <f>I16*18%</f>
+        <v>11331.9</v>
+      </c>
+      <c r="M16" s="105">
+        <f>I16-K16-L16</f>
+        <v>51623.1</v>
+      </c>
+      <c r="N16" s="105">
+        <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
+        <v>9292.1579999999994</v>
+      </c>
+      <c r="O16" s="106">
+        <f>(N16+M16)*$O$15</f>
+        <v>304.57629000000003</v>
+      </c>
+      <c r="P16" s="104">
+        <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
+        <v>61219.834289999999</v>
+      </c>
+      <c r="Q16" s="107"/>
+      <c r="XFD16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A17" s="108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="109" t="str">
+        <f>VLOOKUP($A17,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Lemon Tarka</v>
+      </c>
+      <c r="C17" s="110">
+        <f>VLOOKUP(B17,'[1]Cust. Price List'!E7:P15,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D17" s="111">
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E17" s="111">
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F17" s="112">
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G17" s="113"/>
+      <c r="H17" s="114">
+        <v>1200</v>
+      </c>
+      <c r="I17" s="115">
+        <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
+        <v>62955</v>
+      </c>
+      <c r="J17" s="116">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="104">
+        <f t="shared" ref="L17:L21" si="4">I17*18%</f>
+        <v>11331.9</v>
+      </c>
+      <c r="M17" s="117">
+        <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
+        <v>51623.1</v>
+      </c>
+      <c r="N17" s="117">
+        <f t="shared" si="0"/>
+        <v>9292.1579999999994</v>
+      </c>
+      <c r="O17" s="118">
+        <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
+        <v>304.57629000000003</v>
+      </c>
+      <c r="P17" s="119">
+        <f t="shared" si="1"/>
+        <v>61219.834289999999</v>
+      </c>
+      <c r="S17" s="64"/>
+      <c r="XFD17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A18" s="108" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="109" t="str">
+        <f>VLOOKUP($A18,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Chicken Chatkhara</v>
+      </c>
+      <c r="C18" s="110">
+        <f>VLOOKUP(B18,'[1]Cust. Price List'!E8:P16,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="D18" s="111">
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E18" s="111">
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,6,0)</f>
+        <v>65</v>
+      </c>
+      <c r="F18" s="112">
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,10,0)</f>
+        <v>52.462499999999999</v>
+      </c>
+      <c r="G18" s="113"/>
+      <c r="H18" s="114">
+        <v>1800</v>
+      </c>
+      <c r="I18" s="115">
+        <f t="shared" si="2"/>
+        <v>94432.5</v>
+      </c>
+      <c r="J18" s="116">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="104">
+        <f t="shared" si="4"/>
+        <v>16997.849999999999</v>
+      </c>
+      <c r="M18" s="117">
+        <f t="shared" si="5"/>
+        <v>77434.649999999994</v>
+      </c>
+      <c r="N18" s="117">
+        <f t="shared" si="0"/>
+        <v>13938.236999999999</v>
+      </c>
+      <c r="O18" s="118">
+        <f t="shared" si="6"/>
+        <v>456.86443499999996</v>
+      </c>
+      <c r="P18" s="119">
+        <f t="shared" si="1"/>
+        <v>91829.751434999984</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A19" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="109" t="str">
+        <f>VLOOKUP($A19,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Meat Masala (Jumbo)</v>
+      </c>
+      <c r="C19" s="110">
+        <f>VLOOKUP(B19,'[1]Cust. Price List'!E9:P17,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="D19" s="111">
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E19" s="111">
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="F19" s="112">
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,10,0)</f>
+        <v>72.64</v>
+      </c>
+      <c r="G19" s="113"/>
+      <c r="H19" s="114">
+        <v>2400</v>
+      </c>
+      <c r="I19" s="115">
+        <f t="shared" si="2"/>
+        <v>174336</v>
+      </c>
+      <c r="J19" s="116">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="104">
+        <f t="shared" si="4"/>
+        <v>31380.48</v>
+      </c>
+      <c r="M19" s="117">
+        <f t="shared" si="5"/>
+        <v>142955.51999999999</v>
+      </c>
+      <c r="N19" s="117">
+        <f t="shared" si="0"/>
+        <v>25731.993599999998</v>
+      </c>
+      <c r="O19" s="118">
+        <f t="shared" si="6"/>
+        <v>843.43756799999994</v>
+      </c>
+      <c r="P19" s="119">
+        <f t="shared" si="1"/>
+        <v>169530.95116799997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A20" s="108" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="109" t="str">
+        <f>VLOOKUP($A20,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Lemon Tarka (Jumbo)</v>
+      </c>
+      <c r="C20" s="110">
+        <f>VLOOKUP(B20,'[1]Cust. Price List'!E10:P18,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="D20" s="111">
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E20" s="111">
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="F20" s="112">
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,10,0)</f>
+        <v>72.64</v>
+      </c>
+      <c r="G20" s="113"/>
+      <c r="H20" s="114">
+        <v>1800</v>
+      </c>
+      <c r="I20" s="115">
+        <f t="shared" si="2"/>
+        <v>130752</v>
+      </c>
+      <c r="J20" s="116">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="104">
+        <f t="shared" si="4"/>
+        <v>23535.360000000001</v>
+      </c>
+      <c r="M20" s="117">
+        <f t="shared" si="5"/>
+        <v>107216.64</v>
+      </c>
+      <c r="N20" s="117">
+        <f t="shared" si="0"/>
+        <v>19298.995199999998</v>
+      </c>
+      <c r="O20" s="118">
+        <f t="shared" si="6"/>
+        <v>632.57817599999998</v>
+      </c>
+      <c r="P20" s="119">
+        <f t="shared" si="1"/>
+        <v>127148.21337599999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A21" s="108" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="109" t="str">
+        <f>VLOOKUP($A21,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Chicken Chatkhara (Jumbo)</v>
+      </c>
+      <c r="C21" s="110">
+        <f>VLOOKUP(B21,'[1]Cust. Price List'!E11:P19,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="D21" s="111">
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E21" s="111">
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,6,0)</f>
+        <v>90</v>
+      </c>
+      <c r="F21" s="112">
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,10,0)</f>
+        <v>72.64</v>
+      </c>
+      <c r="G21" s="113"/>
+      <c r="H21" s="114">
+        <v>1800</v>
+      </c>
+      <c r="I21" s="115">
+        <f t="shared" si="2"/>
+        <v>130752</v>
+      </c>
+      <c r="J21" s="116">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="104">
+        <f t="shared" si="4"/>
+        <v>23535.360000000001</v>
+      </c>
+      <c r="M21" s="117">
+        <f t="shared" si="5"/>
+        <v>107216.64</v>
+      </c>
+      <c r="N21" s="117">
+        <f t="shared" si="0"/>
+        <v>19298.995199999998</v>
+      </c>
+      <c r="O21" s="118">
+        <f t="shared" si="6"/>
+        <v>632.57817599999998</v>
+      </c>
+      <c r="P21" s="119">
+        <f t="shared" si="1"/>
+        <v>127148.21337599999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A22" s="108" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="109" t="str">
+        <f>VLOOKUP($A22,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Chicken Chatkhara  (ECO)</v>
+      </c>
+      <c r="C22" s="110">
+        <f>VLOOKUP(B22,'[1]Cust. Price List'!E12:P20,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="D22" s="111">
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E22" s="111">
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,6,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F22" s="120">
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,10,0)</f>
+        <v>39.230000000000004</v>
+      </c>
+      <c r="G22" s="113"/>
+      <c r="H22" s="114">
+        <v>0</v>
+      </c>
+      <c r="I22" s="115">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="116"/>
+      <c r="K22" s="1">
+        <f>I22*3.5%</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="119">
+        <f>I22*5%</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="117">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="117">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A23" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="109" t="str">
+        <f>VLOOKUP($A23,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Lemon Tarka (ECO)</v>
+      </c>
+      <c r="C23" s="110">
+        <f>VLOOKUP(B23,'[1]Cust. Price List'!E13:P21,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="D23" s="111">
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E23" s="111">
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,6,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F23" s="112">
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,10,0)</f>
+        <v>39.230000000000004</v>
+      </c>
+      <c r="G23" s="113"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="115">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="116"/>
+      <c r="K23" s="1">
+        <f t="shared" ref="K23:K24" si="7">I23*3.5%</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="119">
+        <f t="shared" ref="L23:L24" si="8">I23*$L$13</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="117">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="117">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="118">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="122" t="str">
+        <f>VLOOKUP($A24,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <v>Meat Masala (ECO)</v>
+      </c>
+      <c r="C24" s="123">
+        <f>VLOOKUP(B24,'[1]Cust. Price List'!E14:P22,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="D24" s="124">
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,4,0)</f>
+        <v>40</v>
+      </c>
+      <c r="E24" s="124">
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,6,0)</f>
+        <v>50</v>
+      </c>
+      <c r="F24" s="125">
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,10,0)</f>
+        <v>39.230000000000004</v>
+      </c>
+      <c r="G24" s="126"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="128">
+        <f>(G24*D24)*F24+H24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="129"/>
+      <c r="K24" s="130">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="131">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="132">
+        <f>I24-K24-L24</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="132">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="133">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="131">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="210" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="211"/>
+      <c r="C25" s="212"/>
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="247"/>
+      <c r="G25" s="134">
+        <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="135">
+        <f t="shared" si="9"/>
+        <v>10200</v>
+      </c>
+      <c r="I25" s="136">
+        <f t="shared" si="9"/>
+        <v>656182.5</v>
+      </c>
+      <c r="J25" s="137"/>
+      <c r="K25" s="138">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="139">
+        <f t="shared" si="9"/>
+        <v>118112.84999999999</v>
+      </c>
+      <c r="M25" s="140">
+        <f t="shared" si="9"/>
+        <v>538069.65</v>
+      </c>
+      <c r="N25" s="141">
+        <f>SUM(N16:N24)</f>
+        <v>96852.537000000011</v>
+      </c>
+      <c r="O25" s="142">
+        <f>SUM(O16:O24)</f>
+        <v>3174.6109349999997</v>
+      </c>
+      <c r="P25" s="143">
+        <f>SUM(P16:P24)</f>
+        <v>638096.79793499992</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="A26" s="144"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="145"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="146"/>
+      <c r="K26" s="147"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="147"/>
+      <c r="N26" s="147"/>
+      <c r="O26" s="148"/>
+      <c r="P26" s="147"/>
+    </row>
+    <row r="27" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="69"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+    </row>
+    <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
+      <c r="B28" s="213" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="214"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="214"/>
+      <c r="F28" s="214"/>
+      <c r="G28" s="214"/>
+      <c r="H28" s="214"/>
+      <c r="I28" s="214"/>
+      <c r="J28" s="214"/>
+      <c r="K28" s="214"/>
+      <c r="L28" s="215"/>
+      <c r="N28" s="222" t="s">
+        <v>86</v>
+      </c>
+      <c r="O28" s="223"/>
+      <c r="P28" s="151">
+        <f>I25</f>
+        <v>656182.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="216"/>
+      <c r="C29" s="217"/>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="217"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="217"/>
+      <c r="J29" s="217"/>
+      <c r="K29" s="217"/>
+      <c r="L29" s="218"/>
+      <c r="N29" s="224" t="s">
+        <v>87</v>
+      </c>
+      <c r="O29" s="225"/>
+      <c r="P29" s="152">
+        <f>L25</f>
+        <v>118112.84999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="216"/>
+      <c r="C30" s="217"/>
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="217"/>
+      <c r="J30" s="217"/>
+      <c r="K30" s="217"/>
+      <c r="L30" s="218"/>
+      <c r="N30" s="224" t="s">
+        <v>4</v>
+      </c>
+      <c r="O30" s="225"/>
+      <c r="P30" s="153">
+        <f>K25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="216"/>
+      <c r="C31" s="217"/>
+      <c r="D31" s="217"/>
+      <c r="E31" s="217"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="217"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="217"/>
+      <c r="J31" s="217"/>
+      <c r="K31" s="217"/>
+      <c r="L31" s="218"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="224" t="s">
+        <v>88</v>
+      </c>
+      <c r="O31" s="225"/>
+      <c r="P31" s="152">
+        <f>P28-P29-P30</f>
+        <v>538069.65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="216"/>
+      <c r="C32" s="217"/>
+      <c r="D32" s="217"/>
+      <c r="E32" s="217"/>
+      <c r="F32" s="217"/>
+      <c r="G32" s="217"/>
+      <c r="H32" s="217"/>
+      <c r="I32" s="217"/>
+      <c r="J32" s="217"/>
+      <c r="K32" s="217"/>
+      <c r="L32" s="218"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="154" t="s">
+        <v>89</v>
+      </c>
+      <c r="O32" s="155">
+        <f>IF(B12="Registered",18%,22%)</f>
+        <v>0.18</v>
+      </c>
+      <c r="P32" s="152">
+        <f>N25</f>
+        <v>96852.537000000011</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="216"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="218"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="226" t="s">
+        <v>90</v>
+      </c>
+      <c r="O33" s="227"/>
+      <c r="P33" s="152">
+        <f>P31+P32</f>
+        <v>634922.18700000003</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="219"/>
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="220"/>
+      <c r="F34" s="220"/>
+      <c r="G34" s="220"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="220"/>
+      <c r="J34" s="220"/>
+      <c r="K34" s="220"/>
+      <c r="L34" s="221"/>
+      <c r="M34" s="156"/>
+      <c r="N34" s="157" t="s">
+        <v>91</v>
+      </c>
+      <c r="O34" s="158">
+        <f>IF(B11="Filer",0.5%,2.5%)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P34" s="152">
+        <f>O34*P33</f>
+        <v>3174.6109350000002</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N35" s="204" t="s">
+        <v>92</v>
+      </c>
+      <c r="O35" s="205"/>
+      <c r="P35" s="159">
+        <f>P33+P34</f>
+        <v>638096.79793500004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27585,1253 +28830,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:XFD37"/>
-  <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10" style="69" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="246" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="246"/>
-      <c r="C2" s="246"/>
-    </row>
-    <row r="3" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="231" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="71"/>
-      <c r="K3" s="230" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" s="230"/>
-      <c r="M3" s="230"/>
-      <c r="N3" s="231">
-        <v>2</v>
-      </c>
-      <c r="O3" s="231"/>
-      <c r="P3" s="231"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="71"/>
-      <c r="XFC3" t="s">
-        <v>48</v>
-      </c>
-      <c r="XFD3" s="72">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="231" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="231"/>
-      <c r="C4" s="231"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="K4" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="230"/>
-      <c r="M4" s="230"/>
-      <c r="N4" s="244">
-        <f ca="1">TODAY()</f>
-        <v>46212</v>
-      </c>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="R4" s="70"/>
-      <c r="S4" s="71"/>
-      <c r="XFC4" s="73" t="s">
-        <v>50</v>
-      </c>
-      <c r="XFD4" s="72">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="253" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="253"/>
-      <c r="C5" s="253"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="71"/>
-      <c r="K5" s="230" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="230"/>
-      <c r="M5" s="230"/>
-      <c r="N5" s="244">
-        <f ca="1">N4-1</f>
-        <v>46211</v>
-      </c>
-      <c r="O5" s="231"/>
-      <c r="P5" s="231"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="71"/>
-    </row>
-    <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="230" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="230"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="74"/>
-      <c r="K6" s="230" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="230"/>
-      <c r="M6" s="230"/>
-      <c r="N6" s="243" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="243"/>
-      <c r="P6" s="243"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="74"/>
-      <c r="XFC6" t="s">
-        <v>53</v>
-      </c>
-      <c r="XFD6" s="2">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19 16383:16384" s="73" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="230"/>
-      <c r="B7" s="230"/>
-      <c r="C7" s="230"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="74"/>
-      <c r="K7" s="230"/>
-      <c r="L7" s="230"/>
-      <c r="M7" s="230"/>
-      <c r="N7" s="243"/>
-      <c r="O7" s="243"/>
-      <c r="P7" s="243"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="74"/>
-      <c r="XFC7" t="s">
-        <v>54</v>
-      </c>
-      <c r="XFD7" s="2">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="242"/>
-      <c r="B8" s="242"/>
-      <c r="C8" s="242"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="74"/>
-      <c r="K8" s="230"/>
-      <c r="L8" s="230"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="243"/>
-      <c r="O8" s="243"/>
-      <c r="P8" s="243"/>
-      <c r="R8" s="70"/>
-      <c r="S8" s="74"/>
-    </row>
-    <row r="9" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="242"/>
-      <c r="B9" s="242"/>
-      <c r="C9" s="242"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="74"/>
-      <c r="K9" s="230"/>
-      <c r="L9" s="230"/>
-      <c r="M9" s="230"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="243"/>
-      <c r="P9" s="243"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="74"/>
-      <c r="XFD9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="228" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="75" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="75"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
-      <c r="K10" s="230" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" s="230"/>
-      <c r="M10" s="230"/>
-      <c r="N10" s="231" t="s">
-        <v>57</v>
-      </c>
-      <c r="O10" s="231"/>
-      <c r="P10" s="231"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="71"/>
-      <c r="XFD10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A11" s="228"/>
-      <c r="B11" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="77" t="str">
-        <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
-      </c>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
-      <c r="K11" s="230" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="230"/>
-      <c r="M11" s="230"/>
-      <c r="N11" s="231" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" s="231"/>
-      <c r="P11" s="231"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="71"/>
-    </row>
-    <row r="12" spans="1:19 16383:16384" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="228" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="77" t="str">
-        <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
-      </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="71"/>
-      <c r="K12" s="230" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="230"/>
-      <c r="M12" s="230"/>
-      <c r="N12" s="231"/>
-      <c r="O12" s="231"/>
-      <c r="P12" s="231"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="71"/>
-      <c r="XFD12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="229"/>
-      <c r="B13" s="167">
-        <v>300426949714</v>
-      </c>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="79">
-        <v>0.05</v>
-      </c>
-      <c r="XFD13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19 16383:16384" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="232" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="236" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="82" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="248" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="249"/>
-      <c r="I14" s="250" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="248" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="252"/>
-      <c r="L14" s="249"/>
-      <c r="M14" s="250" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="P14" s="85" t="s">
-        <v>74</v>
-      </c>
-      <c r="XFD14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="234"/>
-      <c r="B15" s="235"/>
-      <c r="C15" s="237"/>
-      <c r="D15" s="86" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="86" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="87" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="88" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15" s="89" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="251"/>
-      <c r="J15" s="88" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="90" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" s="183">
-        <v>0.18</v>
-      </c>
-      <c r="M15" s="251"/>
-      <c r="N15" s="91">
-        <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
-      </c>
-      <c r="O15" s="92">
-        <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="P15" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="XFD15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A16" s="94" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="95" t="str">
-        <f>VLOOKUP($A16,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v xml:space="preserve">Meat Masala </v>
-      </c>
-      <c r="C16" s="96">
-        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,3,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D16" s="97">
-        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E16" s="97">
-        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F16" s="98">
-        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>0</v>
-      </c>
-      <c r="I16" s="101">
-        <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="102">
-        <v>0</v>
-      </c>
-      <c r="K16" s="103">
-        <f>I16*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="104">
-        <f>I16*18%</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="105">
-        <f>I16-K16-L16</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="105">
-        <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="106">
-        <f>(N16+M16)*$O$15</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="104">
-        <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="107"/>
-      <c r="XFD16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A17" s="108" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="109" t="str">
-        <f>VLOOKUP($A17,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka</v>
-      </c>
-      <c r="C17" s="110">
-        <f>VLOOKUP(B17,'[1]Cust. Price List'!E7:P15,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D17" s="111">
-        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E17" s="111">
-        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F17" s="112">
-        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G17" s="113"/>
-      <c r="H17" s="114">
-        <v>0</v>
-      </c>
-      <c r="I17" s="115">
-        <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="116">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="4">I17*18%</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="117">
-        <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="118">
-        <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="64"/>
-      <c r="XFD17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A18" s="108" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="109" t="str">
-        <f>VLOOKUP($A18,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara</v>
-      </c>
-      <c r="C18" s="110">
-        <f>VLOOKUP(B18,'[1]Cust. Price List'!E8:P16,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D18" s="111">
-        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E18" s="111">
-        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F18" s="112">
-        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,10,0)</f>
-        <v>52.462499999999999</v>
-      </c>
-      <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>0</v>
-      </c>
-      <c r="I18" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="104">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A19" s="108" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="109" t="str">
-        <f>VLOOKUP($A19,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Meat Masala (Jumbo)</v>
-      </c>
-      <c r="C19" s="110">
-        <f>VLOOKUP(B19,'[1]Cust. Price List'!E9:P17,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D19" s="111">
-        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E19" s="111">
-        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F19" s="112">
-        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,10,0)</f>
-        <v>72.64</v>
-      </c>
-      <c r="G19" s="113"/>
-      <c r="H19" s="114">
-        <v>0</v>
-      </c>
-      <c r="I19" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="104">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A20" s="108" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="109" t="str">
-        <f>VLOOKUP($A20,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (Jumbo)</v>
-      </c>
-      <c r="C20" s="110">
-        <f>VLOOKUP(B20,'[1]Cust. Price List'!E10:P18,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D20" s="111">
-        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E20" s="111">
-        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F20" s="112">
-        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,10,0)</f>
-        <v>72.64</v>
-      </c>
-      <c r="G20" s="113"/>
-      <c r="H20" s="114">
-        <v>0</v>
-      </c>
-      <c r="I20" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="104">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A21" s="108" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="109" t="str">
-        <f>VLOOKUP($A21,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara (Jumbo)</v>
-      </c>
-      <c r="C21" s="110">
-        <f>VLOOKUP(B21,'[1]Cust. Price List'!E11:P19,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D21" s="111">
-        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E21" s="111">
-        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F21" s="112">
-        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,10,0)</f>
-        <v>72.64</v>
-      </c>
-      <c r="G21" s="113"/>
-      <c r="H21" s="114">
-        <v>0</v>
-      </c>
-      <c r="I21" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="104">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A22" s="108" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="109" t="str">
-        <f>VLOOKUP($A22,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara  (ECO)</v>
-      </c>
-      <c r="C22" s="110">
-        <f>VLOOKUP(B22,'[1]Cust. Price List'!E12:P20,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D22" s="111">
-        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E22" s="111">
-        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F22" s="120">
-        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,10,0)</f>
-        <v>39.230000000000004</v>
-      </c>
-      <c r="G22" s="113"/>
-      <c r="H22" s="114">
-        <v>0</v>
-      </c>
-      <c r="I22" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="116"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="119">
-        <f>I22*5%</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A23" s="108" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="109" t="str">
-        <f>VLOOKUP($A23,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
-      </c>
-      <c r="C23" s="110">
-        <f>VLOOKUP(B23,'[1]Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D23" s="111">
-        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E23" s="111">
-        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F23" s="112">
-        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
-      </c>
-      <c r="G23" s="113"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="115">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="116"/>
-      <c r="K23" s="1">
-        <f t="shared" ref="K23:K24" si="7">I23*3.5%</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="119">
-        <f t="shared" ref="L23:L24" si="8">I23*$L$13</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="117">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="118">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="121" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="122" t="str">
-        <f>VLOOKUP($A24,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Meat Masala (ECO)</v>
-      </c>
-      <c r="C24" s="123">
-        <f>VLOOKUP(B24,'[1]Cust. Price List'!E14:P22,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D24" s="124">
-        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E24" s="124">
-        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F24" s="125">
-        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
-      </c>
-      <c r="G24" s="126"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="128">
-        <f>(G24*D24)*F24+H24*F24</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="129"/>
-      <c r="K24" s="130">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="131">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="132">
-        <f>I24-K24-L24</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="132">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="133">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="131">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="210" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="211"/>
-      <c r="C25" s="212"/>
-      <c r="D25" s="206"/>
-      <c r="E25" s="206"/>
-      <c r="F25" s="247"/>
-      <c r="G25" s="134">
-        <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="135">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="136">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="137"/>
-      <c r="K25" s="138">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="139">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="140">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="141">
-        <f>SUM(N16:N24)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="142">
-        <f>SUM(O16:O24)</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="143">
-        <f>SUM(P16:P24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="A26" s="144"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="145"/>
-      <c r="H26" s="145"/>
-      <c r="I26" s="146"/>
-      <c r="K26" s="147"/>
-      <c r="L26" s="147"/>
-      <c r="M26" s="147"/>
-      <c r="N26" s="147"/>
-      <c r="O26" s="148"/>
-      <c r="P26" s="147"/>
-    </row>
-    <row r="27" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="69"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
-      <c r="G27" s="150"/>
-      <c r="H27" s="150"/>
-    </row>
-    <row r="28" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="213" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="214"/>
-      <c r="D28" s="214"/>
-      <c r="E28" s="214"/>
-      <c r="F28" s="214"/>
-      <c r="G28" s="214"/>
-      <c r="H28" s="214"/>
-      <c r="I28" s="214"/>
-      <c r="J28" s="214"/>
-      <c r="K28" s="214"/>
-      <c r="L28" s="215"/>
-      <c r="N28" s="222" t="s">
-        <v>86</v>
-      </c>
-      <c r="O28" s="223"/>
-      <c r="P28" s="151">
-        <f>I25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="216"/>
-      <c r="C29" s="217"/>
-      <c r="D29" s="217"/>
-      <c r="E29" s="217"/>
-      <c r="F29" s="217"/>
-      <c r="G29" s="217"/>
-      <c r="H29" s="217"/>
-      <c r="I29" s="217"/>
-      <c r="J29" s="217"/>
-      <c r="K29" s="217"/>
-      <c r="L29" s="218"/>
-      <c r="N29" s="224" t="s">
-        <v>87</v>
-      </c>
-      <c r="O29" s="225"/>
-      <c r="P29" s="152">
-        <f>L25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="216"/>
-      <c r="C30" s="217"/>
-      <c r="D30" s="217"/>
-      <c r="E30" s="217"/>
-      <c r="F30" s="217"/>
-      <c r="G30" s="217"/>
-      <c r="H30" s="217"/>
-      <c r="I30" s="217"/>
-      <c r="J30" s="217"/>
-      <c r="K30" s="217"/>
-      <c r="L30" s="218"/>
-      <c r="N30" s="224" t="s">
-        <v>4</v>
-      </c>
-      <c r="O30" s="225"/>
-      <c r="P30" s="153">
-        <f>K25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="216"/>
-      <c r="C31" s="217"/>
-      <c r="D31" s="217"/>
-      <c r="E31" s="217"/>
-      <c r="F31" s="217"/>
-      <c r="G31" s="217"/>
-      <c r="H31" s="217"/>
-      <c r="I31" s="217"/>
-      <c r="J31" s="217"/>
-      <c r="K31" s="217"/>
-      <c r="L31" s="218"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="224" t="s">
-        <v>88</v>
-      </c>
-      <c r="O31" s="225"/>
-      <c r="P31" s="152">
-        <f>P28-P29-P30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="216"/>
-      <c r="C32" s="217"/>
-      <c r="D32" s="217"/>
-      <c r="E32" s="217"/>
-      <c r="F32" s="217"/>
-      <c r="G32" s="217"/>
-      <c r="H32" s="217"/>
-      <c r="I32" s="217"/>
-      <c r="J32" s="217"/>
-      <c r="K32" s="217"/>
-      <c r="L32" s="218"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="154" t="s">
-        <v>89</v>
-      </c>
-      <c r="O32" s="155">
-        <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
-      </c>
-      <c r="P32" s="152">
-        <f>N25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="216"/>
-      <c r="C33" s="217"/>
-      <c r="D33" s="217"/>
-      <c r="E33" s="217"/>
-      <c r="F33" s="217"/>
-      <c r="G33" s="217"/>
-      <c r="H33" s="217"/>
-      <c r="I33" s="217"/>
-      <c r="J33" s="217"/>
-      <c r="K33" s="217"/>
-      <c r="L33" s="218"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="226" t="s">
-        <v>90</v>
-      </c>
-      <c r="O33" s="227"/>
-      <c r="P33" s="152">
-        <f>P31+P32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="219"/>
-      <c r="C34" s="220"/>
-      <c r="D34" s="220"/>
-      <c r="E34" s="220"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="220"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="220"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="220"/>
-      <c r="L34" s="221"/>
-      <c r="M34" s="156"/>
-      <c r="N34" s="157" t="s">
-        <v>91</v>
-      </c>
-      <c r="O34" s="158">
-        <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="P34" s="152">
-        <f>O34*P33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="204" t="s">
-        <v>92</v>
-      </c>
-      <c r="O35" s="205"/>
-      <c r="P35" s="159">
-        <f>P33+P34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="160" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="206"/>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="206"/>
-      <c r="H36" s="206"/>
-      <c r="I36" s="207"/>
-      <c r="J36" s="208"/>
-      <c r="K36" s="209"/>
-    </row>
-    <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="B28:L34"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>$XFD$12:$XFD$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{00000000-0002-0000-0400-000001000000}">
-      <formula1>$XFC$6:$XFC$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0400-000002000000}">
-      <formula1>$XFC$3:$XFC$4</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000003000000}">
-          <x14:formula1>
-            <xm:f>Sheet2!$B$6:$B$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>N6:P6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
@@ -28907,7 +28905,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28935,7 +28933,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30154,7 +30152,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30182,7 +30180,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31402,7 +31400,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31430,7 +31428,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
